--- a/XLSX/Ball.xlsx
+++ b/XLSX/Ball.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\dodge-ball\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CAE7A0-6346-4BCE-A568-9416D364AAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E701C93-970C-403C-AB09-BF5DF53E96D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="+Ball" sheetId="1" r:id="rId1"/>
@@ -476,7 +476,7 @@
         <v>100</v>
       </c>
       <c r="C3" s="1">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
@@ -490,7 +490,7 @@
         <v>200</v>
       </c>
       <c r="C4" s="1">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -504,7 +504,7 @@
         <v>300</v>
       </c>
       <c r="C5">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
@@ -518,7 +518,7 @@
         <v>400</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
@@ -532,7 +532,7 @@
         <v>500</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>
